--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486376_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486376_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1407</v>
+        <v>4.3346</v>
       </c>
       <c r="E2" t="n">
-        <v>3.0237</v>
+        <v>3.3409</v>
       </c>
       <c r="F2" t="n">
-        <v>1.117</v>
+        <v>0.9937</v>
       </c>
       <c r="G2" t="n">
         <v>0.4556</v>
@@ -610,13 +610,13 @@
         <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7073</v>
+        <v>0.9013</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.0769</v>
+        <v>0.2403</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7842</v>
+        <v>0.6609</v>
       </c>
       <c r="V2" t="n">
         <v>1.8902</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>L. SMITH</t>
+          <t>O. MATULIONIS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4732</v>
+        <v>1.5673</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.2573</v>
+        <v>-1.8774</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7305</v>
+        <v>3.4446</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1284</v>
+        <v>-0.9302</v>
       </c>
       <c r="H3" t="n">
-        <v>2.7341</v>
+        <v>-1.0434</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.6056</v>
+        <v>0.1131</v>
       </c>
       <c r="J3" t="n">
-        <v>2.4872</v>
+        <v>-1.4982</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3724</v>
+        <v>-0.9061</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1147</v>
+        <v>-0.5921</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3587</v>
+        <v>0.5679</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3617</v>
+        <v>-0.1372</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7204</v>
+        <v>0.7052</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.6101</v>
+        <v>-0.2175</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>2.7591</v>
+        <v>-0.0643</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3447</v>
+        <v>-0.3569</v>
       </c>
       <c r="U3" t="n">
-        <v>1.4144</v>
+        <v>0.2926</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.1093</v>
+        <v>0.8218</v>
       </c>
       <c r="W3" t="n">
-        <v>-1.479</v>
+        <v>0.1952</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3698</v>
+        <v>0.6264999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. BOMBINO PARADA</t>
+          <t>L. MENUGE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8596</v>
+        <v>1.4289</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8551</v>
+        <v>0.5507</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0045</v>
+        <v>0.8782</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5153</v>
+        <v>1.6132</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.4313</v>
+        <v>0.3709</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9466</v>
+        <v>1.2423</v>
       </c>
       <c r="J4" t="n">
-        <v>1.0725</v>
+        <v>1.3535</v>
       </c>
       <c r="K4" t="n">
-        <v>0.384</v>
+        <v>0.0912</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6885</v>
+        <v>1.2622</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5572</v>
+        <v>0.2597</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8153</v>
+        <v>0.2796</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2582</v>
+        <v>-0.0199</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.5225</v>
+        <v>0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2626</v>
+        <v>-0.435</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S4" t="n">
-        <v>2.0244</v>
+        <v>0.2932</v>
       </c>
       <c r="T4" t="n">
-        <v>2.0898</v>
+        <v>-0.3677</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0654</v>
+        <v>0.6609</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8424</v>
+        <v>-1.13</v>
       </c>
       <c r="W4" t="n">
-        <v>0.9554</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.113</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. MENUGE</t>
+          <t>L. SMITH</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6185</v>
+        <v>1.1411</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3705</v>
+        <v>-1.2811</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2481</v>
+        <v>2.4222</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6132</v>
+        <v>2.1284</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3709</v>
+        <v>2.7341</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2423</v>
+        <v>-0.6056</v>
       </c>
       <c r="J5" t="n">
-        <v>1.3535</v>
+        <v>2.4872</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0912</v>
+        <v>2.3724</v>
       </c>
       <c r="L5" t="n">
-        <v>1.2622</v>
+        <v>0.1147</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2597</v>
+        <v>-0.3587</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2796</v>
+        <v>0.3617</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0199</v>
+        <v>-0.7204</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6525</v>
+        <v>-1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.435</v>
+        <v>-2.6101</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0875</v>
+        <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4828</v>
+        <v>1.427</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.548</v>
+        <v>0.3209</v>
       </c>
       <c r="U5" t="n">
-        <v>1.0308</v>
+        <v>1.1061</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.13</v>
+        <v>-1.1093</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>-1.479</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.13</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>O. MATULIONIS</t>
+          <t>L. BRACEY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0131</v>
+        <v>0.7835</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.7534</v>
+        <v>0.7755</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7665</v>
+        <v>0.0081</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9302</v>
+        <v>-2.2792</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.0434</v>
+        <v>-1.621</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1131</v>
+        <v>-0.6582</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.4982</v>
+        <v>-1.6502</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.9061</v>
+        <v>-0.7538</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5921</v>
+        <v>-0.8964</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5679</v>
+        <v>-0.629</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1372</v>
+        <v>-0.8672</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7052</v>
+        <v>0.2382</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7401</v>
+        <v>0.6525</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>-1.5225</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9576</v>
+        <v>2.1751</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.6184</v>
+        <v>-0.6715</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.2329</v>
+        <v>-0.2019</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3855</v>
+        <v>-0.4696</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8218</v>
+        <v>3.0817</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1952</v>
+        <v>4.1501</v>
       </c>
       <c r="X6" t="n">
-        <v>0.6264999999999999</v>
+        <v>-1.0684</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. BRACEY</t>
+          <t>P. BOMBINO PARADA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6551</v>
+        <v>0.0437</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3241</v>
+        <v>-0.5293</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.331</v>
+        <v>0.573</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2792</v>
+        <v>0.5153</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.621</v>
+        <v>-0.4313</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6582</v>
+        <v>0.9466</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.6502</v>
+        <v>1.0725</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7538</v>
+        <v>0.384</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8964</v>
+        <v>0.6885</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.629</v>
+        <v>-0.5572</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8672</v>
+        <v>-0.8153</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2382</v>
+        <v>0.2582</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6525</v>
+        <v>-1.5225</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.5225</v>
+        <v>-3.2626</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1751</v>
+        <v>1.7401</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.1101</v>
+        <v>0.2085</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3014</v>
+        <v>0.7054</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.8086</v>
+        <v>-0.4969</v>
       </c>
       <c r="V7" t="n">
-        <v>3.0817</v>
+        <v>0.8424</v>
       </c>
       <c r="W7" t="n">
-        <v>4.1501</v>
+        <v>0.9554</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.0684</v>
+        <v>-0.113</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. ARAMBURU LAMY</t>
+          <t>J. BOCCA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7985</v>
+        <v>-0.6019</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.416</v>
+        <v>1.568</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3825</v>
+        <v>-2.1699</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0044</v>
+        <v>-0.0316</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4108</v>
+        <v>-0.4746</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4152</v>
+        <v>0.443</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1712</v>
+        <v>1.4706</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1441</v>
+        <v>0.4562</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.9729</v>
+        <v>1.0144</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1756</v>
+        <v>-1.5022</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7333</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4423</v>
+        <v>-0.5714</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.2175</v>
+        <v>1.305</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.9576</v>
+        <v>1.305</v>
       </c>
       <c r="S8" t="n">
-        <v>1.0807</v>
+        <v>-0.6324</v>
       </c>
       <c r="T8" t="n">
-        <v>1.0022</v>
+        <v>0.0973</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0785</v>
+        <v>-0.7297</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6573</v>
+        <v>-1.243</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5857</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>-1.243</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BOCCA</t>
+          <t>J. ARAMBURU LAMY</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.7301</v>
+        <v>-1.3676</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7171999999999999</v>
+        <v>-0.7693</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.4473</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0316</v>
+        <v>-1.0044</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4746</v>
+        <v>0.4108</v>
       </c>
       <c r="I9" t="n">
-        <v>0.443</v>
+        <v>-1.4152</v>
       </c>
       <c r="J9" t="n">
-        <v>1.4706</v>
+        <v>0.1712</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4562</v>
+        <v>1.1441</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0144</v>
+        <v>-0.9729</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.5022</v>
+        <v>-1.1756</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-0.7333</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.5714</v>
+        <v>-0.4423</v>
       </c>
       <c r="P9" t="n">
-        <v>1.305</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>1.305</v>
+        <v>1.9576</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.7606</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7534999999999999</v>
+        <v>0.6489</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0071</v>
+        <v>-0.1373</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.243</v>
+        <v>-0.6573</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5857</v>
       </c>
       <c r="X9" t="n">
         <v>-1.243</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5349</v>
+        <v>-2.5732</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4501</v>
+        <v>-1.6425</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0848</v>
+        <v>-0.9307</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2319</v>
@@ -1234,13 +1234,13 @@
         <v>2.3926</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.2828</v>
+        <v>-0.3212</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2329</v>
+        <v>-0.4254</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0499</v>
+        <v>0.1042</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8902</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.386499999999999</v>
+        <v>4.756399999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.2344</v>
+        <v>0.1355000000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>4.621</v>
+        <v>4.6209</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.7647999999999997</v>
+        <v>-0.7648000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5023000000000001</v>
+        <v>0.5023000000000005</v>
       </c>
       <c r="I11" t="n">
         <v>-1.2671</v>
@@ -1312,13 +1312,13 @@
         <v>15.2255</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2824</v>
+        <v>1.6522</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7089000000000005</v>
+        <v>0.6609</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9913999999999996</v>
+        <v>0.9912000000000004</v>
       </c>
       <c r="V11" t="n">
         <v>0.6063000000000001</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. CAMACHO DE SÁ</t>
+          <t>P. SCRUBB</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.5144</v>
+        <v>4.1308</v>
       </c>
       <c r="E12" t="n">
-        <v>1.5544</v>
+        <v>3.6217</v>
       </c>
       <c r="F12" t="n">
-        <v>1.96</v>
+        <v>0.5091</v>
       </c>
       <c r="G12" t="n">
-        <v>1.7219</v>
+        <v>2.9406</v>
       </c>
       <c r="H12" t="n">
-        <v>1.7059</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0159</v>
+        <v>2.1316</v>
       </c>
       <c r="J12" t="n">
-        <v>1.73</v>
+        <v>3.1002</v>
       </c>
       <c r="K12" t="n">
-        <v>1.8432</v>
+        <v>1.0132</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1131</v>
+        <v>2.087</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.008200000000000001</v>
+        <v>-0.1596</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.1372</v>
+        <v>-0.2042</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1291</v>
+        <v>0.0446</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5225</v>
+        <v>-0.87</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-2.6101</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5225</v>
+        <v>1.7401</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9539</v>
+        <v>-0.2346</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5432</v>
+        <v>-0.2584</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4107</v>
+        <v>0.0237</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6839</v>
+        <v>2.2949</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.7188</v>
+        <v>3.3899</v>
       </c>
       <c r="X12" t="n">
-        <v>0.0349</v>
+        <v>-1.0951</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. SCRUBB</t>
+          <t>H. ATENCIA SUAREZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.2059</v>
+        <v>3.7369</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7276</v>
+        <v>2.0526</v>
       </c>
       <c r="F13" t="n">
-        <v>0.4783</v>
+        <v>1.6843</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9406</v>
+        <v>2.7195</v>
       </c>
       <c r="H13" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.7512</v>
       </c>
       <c r="I13" t="n">
-        <v>2.1316</v>
+        <v>1.9683</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1002</v>
+        <v>2.3811</v>
       </c>
       <c r="K13" t="n">
-        <v>1.0132</v>
+        <v>1.287</v>
       </c>
       <c r="L13" t="n">
-        <v>2.087</v>
+        <v>1.0941</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.1596</v>
+        <v>0.3384</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2042</v>
+        <v>-0.5357</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0446</v>
+        <v>0.8741</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.87</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.6101</v>
+        <v>-2.3926</v>
       </c>
       <c r="R13" t="n">
         <v>1.7401</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1595</v>
+        <v>-0.59</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1524</v>
+        <v>-0.1959</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0071</v>
+        <v>-0.3942</v>
       </c>
       <c r="V13" t="n">
-        <v>2.2949</v>
+        <v>2.2599</v>
       </c>
       <c r="W13" t="n">
-        <v>3.3899</v>
+        <v>2.2599</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0951</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>H. ATENCIA SUAREZ</t>
+          <t>N. CAMACHO DE SÁ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9431</v>
+        <v>2.921</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3821</v>
+        <v>1.3309</v>
       </c>
       <c r="F14" t="n">
-        <v>1.561</v>
+        <v>1.5901</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7195</v>
+        <v>1.7219</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7512</v>
+        <v>1.7059</v>
       </c>
       <c r="I14" t="n">
-        <v>1.9683</v>
+        <v>0.0159</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3811</v>
+        <v>1.73</v>
       </c>
       <c r="K14" t="n">
-        <v>1.287</v>
+        <v>1.8432</v>
       </c>
       <c r="L14" t="n">
-        <v>1.0941</v>
+        <v>-0.1131</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3384</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5357</v>
+        <v>-0.1372</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8741</v>
+        <v>0.1291</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.6525</v>
+        <v>1.5225</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.3926</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7401</v>
+        <v>1.5225</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3839</v>
+        <v>0.3605</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8663999999999999</v>
+        <v>0.3197</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5175</v>
+        <v>0.0408</v>
       </c>
       <c r="V14" t="n">
-        <v>2.2599</v>
+        <v>-0.6839</v>
       </c>
       <c r="W14" t="n">
-        <v>2.2599</v>
+        <v>-0.7188</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.0349</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8918</v>
+        <v>0.6509</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6405999999999999</v>
+        <v>-0.477</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2512</v>
+        <v>1.1279</v>
       </c>
       <c r="G15" t="n">
         <v>2.7628</v>
@@ -1624,13 +1624,13 @@
         <v>1.305</v>
       </c>
       <c r="S15" t="n">
-        <v>1.8994</v>
+        <v>0.6585</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3003</v>
+        <v>0.1827</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5992</v>
+        <v>0.4759</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1603</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. CARRALERO MARTIN</t>
+          <t>A. CHAPELA LAGE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2392</v>
+        <v>-0.6788</v>
       </c>
       <c r="E16" t="n">
-        <v>1.7122</v>
+        <v>-0.8255</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.9514</v>
+        <v>0.1467</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4247</v>
+        <v>-0.3295</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1187</v>
+        <v>0.1216</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.306</v>
+        <v>-0.451</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1544</v>
+        <v>-0.0601</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5141</v>
+        <v>0.073</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6686</v>
+        <v>-0.1331</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.2703</v>
+        <v>-0.2694</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6328</v>
+        <v>0.0486</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3626</v>
+        <v>-0.318</v>
       </c>
       <c r="P16" t="n">
-        <v>1.0875</v>
+        <v>0.2175</v>
       </c>
       <c r="Q16" t="n">
+        <v>-0.2175</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="S16" t="n">
+        <v>-0.3716</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.548</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.1763</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.1952</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.0875</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.4231</v>
-      </c>
-      <c r="T16" t="n">
-        <v>0.7367</v>
-      </c>
-      <c r="U16" t="n">
-        <v>-0.3135</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-1.3252</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.13</v>
-      </c>
       <c r="X16" t="n">
-        <v>-2.4552</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="17">
@@ -1735,10 +1735,10 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.3551</v>
+        <v>-0.6904</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.5593</v>
+        <v>-2.8946</v>
       </c>
       <c r="F17" t="n">
         <v>2.2041</v>
@@ -1780,10 +1780,10 @@
         <v>0.87</v>
       </c>
       <c r="S17" t="n">
-        <v>0.584</v>
+        <v>0.2488</v>
       </c>
       <c r="T17" t="n">
-        <v>0.8051</v>
+        <v>0.4699</v>
       </c>
       <c r="U17" t="n">
         <v>-0.2211</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. CHAPELA LAGE</t>
+          <t>J. CARRALERO MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.8329</v>
+        <v>-0.7672</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8255</v>
+        <v>1.1534</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0074</v>
+        <v>-1.9206</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3295</v>
+        <v>-0.4247</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1216</v>
+        <v>-0.1187</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.451</v>
+        <v>-0.306</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0601</v>
+        <v>-0.1544</v>
       </c>
       <c r="K18" t="n">
-        <v>0.073</v>
+        <v>0.5141</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1331</v>
+        <v>-0.6686</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.2694</v>
+        <v>-0.2703</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0486</v>
+        <v>-0.6328</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.318</v>
+        <v>0.3626</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2175</v>
+        <v>1.0875</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.435</v>
+        <v>1.0875</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5256999999999999</v>
+        <v>-0.1048</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.548</v>
+        <v>0.1779</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0222</v>
+        <v>-0.2827</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1952</v>
+        <v>-1.3252</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1952</v>
+        <v>-2.4552</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.4133</v>
+        <v>-1.4055</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9697</v>
+        <v>-0.7461</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.4436</v>
+        <v>-0.6594</v>
       </c>
       <c r="G19" t="n">
         <v>-0.2215</v>
@@ -1936,13 +1936,13 @@
         <v>1.305</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2364</v>
+        <v>-0.2286</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6609</v>
+        <v>-0.4374</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4245</v>
+        <v>0.2088</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9554</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.6071</v>
+        <v>-2.1408</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0761</v>
+        <v>-0.5174</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.531</v>
+        <v>-1.6234</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3165</v>
@@ -2014,13 +2014,13 @@
         <v>0.87</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2912</v>
+        <v>0.1751</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6044</v>
+        <v>-0.0457</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3133</v>
+        <v>0.2208</v>
       </c>
       <c r="V20" t="n">
         <v>-2.4345</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9165</v>
+        <v>-3.6815</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.1746</v>
+        <v>-2.0628</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.7419</v>
+        <v>-1.6186</v>
       </c>
       <c r="G21" t="n">
         <v>-2.1135</v>
@@ -2092,13 +2092,13 @@
         <v>0.2175</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2603</v>
+        <v>-0.0252</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3425</v>
+        <v>-0.2307</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0822</v>
+        <v>0.2055</v>
       </c>
       <c r="V21" t="n">
         <v>-1.3252</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.5775</v>
+        <v>-5.462</v>
       </c>
       <c r="E22" t="n">
-        <v>-5.0325</v>
+        <v>-5.256</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.545</v>
+        <v>-0.206</v>
       </c>
       <c r="G22" t="n">
         <v>-5.3913</v>
@@ -2170,13 +2170,13 @@
         <v>0.87</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2859</v>
+        <v>-0.1703</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2019</v>
+        <v>-0.4254</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0.2551</v>
       </c>
       <c r="V22" t="n">
         <v>0.9697</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.386400000000001</v>
+        <v>-3.386600000000002</v>
       </c>
       <c r="E23" t="n">
         <v>-4.620799999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>1.2343</v>
+        <v>1.2342</v>
       </c>
       <c r="G23" t="n">
         <v>0.7647000000000004</v>
@@ -2218,13 +2218,13 @@
         <v>-0.5023000000000004</v>
       </c>
       <c r="I23" t="n">
-        <v>1.267</v>
+        <v>1.266999999999999</v>
       </c>
       <c r="J23" t="n">
         <v>4.579199999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>2.2683</v>
+        <v>2.268300000000001</v>
       </c>
       <c r="L23" t="n">
         <v>2.3108</v>
@@ -2248,16 +2248,16 @@
         <v>11.9627</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2825</v>
+        <v>-0.2822000000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9912000000000001</v>
+        <v>-0.9913000000000002</v>
       </c>
       <c r="U23" t="n">
-        <v>0.7089000000000002</v>
+        <v>0.7089</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.6061999999999996</v>
+        <v>-0.6061999999999992</v>
       </c>
       <c r="W23" t="n">
         <v>7.0165</v>
